--- a/output/Single_Comprehensive_Efficiency_Comparison.xlsx
+++ b/output/Single_Comprehensive_Efficiency_Comparison.xlsx
@@ -1489,13 +1489,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0522665714285714</v>
+        <v>0.0525787142857143</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
         <v>79</v>
@@ -1517,13 +1517,13 @@
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8"/>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
+      <c r="S8"/>
       <c r="T8"/>
       <c r="U8"/>
       <c r="V8"/>
-      <c r="W8"/>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
       <c r="X8"/>
       <c r="Y8"/>
       <c r="Z8"/>
@@ -1539,13 +1539,13 @@
       <c r="AJ8"/>
       <c r="AK8"/>
       <c r="AL8"/>
-      <c r="AM8" t="n">
-        <v>0.0522665714285714</v>
-      </c>
+      <c r="AM8"/>
       <c r="AN8"/>
       <c r="AO8"/>
       <c r="AP8"/>
-      <c r="AQ8"/>
+      <c r="AQ8" t="n">
+        <v>0.0525787142857143</v>
+      </c>
       <c r="AR8"/>
       <c r="AS8"/>
       <c r="AT8"/>
@@ -1561,13 +1561,13 @@
       <c r="BD8"/>
       <c r="BE8"/>
       <c r="BF8"/>
-      <c r="BG8" t="n">
-        <v>100</v>
-      </c>
+      <c r="BG8"/>
       <c r="BH8"/>
       <c r="BI8"/>
       <c r="BJ8"/>
-      <c r="BK8"/>
+      <c r="BK8" t="n">
+        <v>100</v>
+      </c>
       <c r="BL8"/>
       <c r="BM8"/>
       <c r="BN8"/>
@@ -1593,7 +1593,7 @@
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
         <v>79</v>
@@ -1619,13 +1619,13 @@
       <c r="T9"/>
       <c r="U9"/>
       <c r="V9"/>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
+      <c r="W9"/>
       <c r="X9"/>
       <c r="Y9"/>
       <c r="Z9"/>
-      <c r="AA9"/>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9"/>
@@ -1641,13 +1641,13 @@
       <c r="AN9"/>
       <c r="AO9"/>
       <c r="AP9"/>
-      <c r="AQ9" t="n">
-        <v>0.0525787142857143</v>
-      </c>
+      <c r="AQ9"/>
       <c r="AR9"/>
       <c r="AS9"/>
       <c r="AT9"/>
-      <c r="AU9"/>
+      <c r="AU9" t="n">
+        <v>0.0525787142857143</v>
+      </c>
       <c r="AV9"/>
       <c r="AW9"/>
       <c r="AX9"/>
@@ -1663,44 +1663,44 @@
       <c r="BH9"/>
       <c r="BI9"/>
       <c r="BJ9"/>
-      <c r="BK9" t="n">
-        <v>100</v>
-      </c>
+      <c r="BK9"/>
       <c r="BL9"/>
       <c r="BM9"/>
       <c r="BN9"/>
-      <c r="BO9"/>
+      <c r="BO9" t="n">
+        <v>100</v>
+      </c>
       <c r="BP9"/>
       <c r="BQ9"/>
       <c r="BR9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>1.14285714285714</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0525787142857143</v>
+        <v>0.444368428571429</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>85.7142857142857</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
         <v>80</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
@@ -1711,7 +1711,9 @@
       <c r="N10"/>
       <c r="O10"/>
       <c r="P10"/>
-      <c r="Q10"/>
+      <c r="Q10" t="n">
+        <v>1.14285714285714</v>
+      </c>
       <c r="R10"/>
       <c r="S10"/>
       <c r="T10"/>
@@ -1721,9 +1723,7 @@
       <c r="X10"/>
       <c r="Y10"/>
       <c r="Z10"/>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA10"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10"/>
@@ -1733,7 +1733,9 @@
       <c r="AH10"/>
       <c r="AI10"/>
       <c r="AJ10"/>
-      <c r="AK10"/>
+      <c r="AK10" t="n">
+        <v>0.444368428571429</v>
+      </c>
       <c r="AL10"/>
       <c r="AM10"/>
       <c r="AN10"/>
@@ -1743,9 +1745,7 @@
       <c r="AR10"/>
       <c r="AS10"/>
       <c r="AT10"/>
-      <c r="AU10" t="n">
-        <v>0.0525787142857143</v>
-      </c>
+      <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10"/>
       <c r="AX10"/>
@@ -1755,7 +1755,9 @@
       <c r="BB10"/>
       <c r="BC10"/>
       <c r="BD10"/>
-      <c r="BE10"/>
+      <c r="BE10" t="n">
+        <v>85.7142857142857</v>
+      </c>
       <c r="BF10"/>
       <c r="BG10"/>
       <c r="BH10"/>
@@ -1765,9 +1767,7 @@
       <c r="BL10"/>
       <c r="BM10"/>
       <c r="BN10"/>
-      <c r="BO10" t="n">
-        <v>100</v>
-      </c>
+      <c r="BO10"/>
       <c r="BP10"/>
       <c r="BQ10"/>
       <c r="BR10"/>
@@ -1783,13 +1783,13 @@
         <v>1.14285714285714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.444368428571429</v>
+        <v>0.443976714285714</v>
       </c>
       <c r="E11" t="n">
         <v>85.7142857142857</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
         <v>72</v>
@@ -1809,9 +1809,7 @@
       <c r="N11"/>
       <c r="O11"/>
       <c r="P11"/>
-      <c r="Q11" t="n">
-        <v>1.14285714285714</v>
-      </c>
+      <c r="Q11"/>
       <c r="R11"/>
       <c r="S11"/>
       <c r="T11"/>
@@ -1819,7 +1817,9 @@
       <c r="V11"/>
       <c r="W11"/>
       <c r="X11"/>
-      <c r="Y11"/>
+      <c r="Y11" t="n">
+        <v>1.14285714285714</v>
+      </c>
       <c r="Z11"/>
       <c r="AA11"/>
       <c r="AB11"/>
@@ -1831,9 +1831,7 @@
       <c r="AH11"/>
       <c r="AI11"/>
       <c r="AJ11"/>
-      <c r="AK11" t="n">
-        <v>0.444368428571429</v>
-      </c>
+      <c r="AK11"/>
       <c r="AL11"/>
       <c r="AM11"/>
       <c r="AN11"/>
@@ -1841,7 +1839,9 @@
       <c r="AP11"/>
       <c r="AQ11"/>
       <c r="AR11"/>
-      <c r="AS11"/>
+      <c r="AS11" t="n">
+        <v>0.443976714285714</v>
+      </c>
       <c r="AT11"/>
       <c r="AU11"/>
       <c r="AV11"/>
@@ -1853,9 +1853,7 @@
       <c r="BB11"/>
       <c r="BC11"/>
       <c r="BD11"/>
-      <c r="BE11" t="n">
-        <v>85.7142857142857</v>
-      </c>
+      <c r="BE11"/>
       <c r="BF11"/>
       <c r="BG11"/>
       <c r="BH11"/>
@@ -1863,7 +1861,9 @@
       <c r="BJ11"/>
       <c r="BK11"/>
       <c r="BL11"/>
-      <c r="BM11"/>
+      <c r="BM11" t="n">
+        <v>85.7142857142857</v>
+      </c>
       <c r="BN11"/>
       <c r="BO11"/>
       <c r="BP11"/>
@@ -1881,13 +1881,13 @@
         <v>1.14285714285714</v>
       </c>
       <c r="D12" t="n">
-        <v>0.443976714285714</v>
+        <v>0.444549714285714</v>
       </c>
       <c r="E12" t="n">
         <v>85.7142857142857</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
         <v>72</v>
@@ -1915,13 +1915,13 @@
       <c r="V12"/>
       <c r="W12"/>
       <c r="X12"/>
-      <c r="Y12" t="n">
-        <v>1.14285714285714</v>
-      </c>
+      <c r="Y12"/>
       <c r="Z12"/>
       <c r="AA12"/>
       <c r="AB12"/>
-      <c r="AC12"/>
+      <c r="AC12" t="n">
+        <v>1.14285714285714</v>
+      </c>
       <c r="AD12"/>
       <c r="AE12"/>
       <c r="AF12"/>
@@ -1937,13 +1937,13 @@
       <c r="AP12"/>
       <c r="AQ12"/>
       <c r="AR12"/>
-      <c r="AS12" t="n">
-        <v>0.443976714285714</v>
-      </c>
+      <c r="AS12"/>
       <c r="AT12"/>
       <c r="AU12"/>
       <c r="AV12"/>
-      <c r="AW12"/>
+      <c r="AW12" t="n">
+        <v>0.444549714285714</v>
+      </c>
       <c r="AX12"/>
       <c r="AY12"/>
       <c r="AZ12"/>
@@ -1959,39 +1959,39 @@
       <c r="BJ12"/>
       <c r="BK12"/>
       <c r="BL12"/>
-      <c r="BM12" t="n">
-        <v>85.7142857142857</v>
-      </c>
+      <c r="BM12"/>
       <c r="BN12"/>
       <c r="BO12"/>
       <c r="BP12"/>
-      <c r="BQ12"/>
+      <c r="BQ12" t="n">
+        <v>85.7142857142857</v>
+      </c>
       <c r="BR12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C13" t="n">
         <v>1.14285714285714</v>
       </c>
       <c r="D13" t="n">
-        <v>0.444549714285714</v>
+        <v>0.0529387142857143</v>
       </c>
       <c r="E13" t="n">
         <v>85.7142857142857</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I13" t="n">
         <v>6</v>
@@ -2000,7 +2000,9 @@
         <v>7</v>
       </c>
       <c r="K13"/>
-      <c r="L13"/>
+      <c r="L13" t="n">
+        <v>1.14285714285714</v>
+      </c>
       <c r="M13"/>
       <c r="N13"/>
       <c r="O13"/>
@@ -2017,12 +2019,12 @@
       <c r="Z13"/>
       <c r="AA13"/>
       <c r="AB13"/>
-      <c r="AC13" t="n">
-        <v>1.14285714285714</v>
-      </c>
+      <c r="AC13"/>
       <c r="AD13"/>
       <c r="AE13"/>
-      <c r="AF13"/>
+      <c r="AF13" t="n">
+        <v>0.0529387142857143</v>
+      </c>
       <c r="AG13"/>
       <c r="AH13"/>
       <c r="AI13"/>
@@ -2039,12 +2041,12 @@
       <c r="AT13"/>
       <c r="AU13"/>
       <c r="AV13"/>
-      <c r="AW13" t="n">
-        <v>0.444549714285714</v>
-      </c>
+      <c r="AW13"/>
       <c r="AX13"/>
       <c r="AY13"/>
-      <c r="AZ13"/>
+      <c r="AZ13" t="n">
+        <v>85.7142857142857</v>
+      </c>
       <c r="BA13"/>
       <c r="BB13"/>
       <c r="BC13"/>
@@ -2061,9 +2063,7 @@
       <c r="BN13"/>
       <c r="BO13"/>
       <c r="BP13"/>
-      <c r="BQ13" t="n">
-        <v>85.7142857142857</v>
-      </c>
+      <c r="BQ13"/>
       <c r="BR13"/>
     </row>
     <row r="14">
@@ -2077,19 +2077,19 @@
         <v>1.14285714285714</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0529387142857143</v>
+        <v>0.0525787142857143</v>
       </c>
       <c r="E14" t="n">
         <v>85.7142857142857</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
         <v>79</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I14" t="n">
         <v>6</v>
@@ -2098,12 +2098,12 @@
         <v>7</v>
       </c>
       <c r="K14"/>
-      <c r="L14" t="n">
-        <v>1.14285714285714</v>
-      </c>
+      <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
-      <c r="O14"/>
+      <c r="O14" t="n">
+        <v>1.14285714285714</v>
+      </c>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
@@ -2120,12 +2120,12 @@
       <c r="AC14"/>
       <c r="AD14"/>
       <c r="AE14"/>
-      <c r="AF14" t="n">
-        <v>0.0529387142857143</v>
-      </c>
+      <c r="AF14"/>
       <c r="AG14"/>
       <c r="AH14"/>
-      <c r="AI14"/>
+      <c r="AI14" t="n">
+        <v>0.0525787142857143</v>
+      </c>
       <c r="AJ14"/>
       <c r="AK14"/>
       <c r="AL14"/>
@@ -2142,12 +2142,12 @@
       <c r="AW14"/>
       <c r="AX14"/>
       <c r="AY14"/>
-      <c r="AZ14" t="n">
-        <v>85.7142857142857</v>
-      </c>
+      <c r="AZ14"/>
       <c r="BA14"/>
       <c r="BB14"/>
-      <c r="BC14"/>
+      <c r="BC14" t="n">
+        <v>85.7142857142857</v>
+      </c>
       <c r="BD14"/>
       <c r="BE14"/>
       <c r="BF14"/>
@@ -2175,13 +2175,13 @@
         <v>1.14285714285714</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0525787142857143</v>
+        <v>0.0522665714285714</v>
       </c>
       <c r="E15" t="n">
         <v>85.7142857142857</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
         <v>79</v>
@@ -2199,13 +2199,13 @@
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15"/>
-      <c r="O15" t="n">
-        <v>1.14285714285714</v>
-      </c>
+      <c r="O15"/>
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15"/>
-      <c r="S15"/>
+      <c r="S15" t="n">
+        <v>1.14285714285714</v>
+      </c>
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15"/>
@@ -2221,13 +2221,13 @@
       <c r="AF15"/>
       <c r="AG15"/>
       <c r="AH15"/>
-      <c r="AI15" t="n">
-        <v>0.0525787142857143</v>
-      </c>
+      <c r="AI15"/>
       <c r="AJ15"/>
       <c r="AK15"/>
       <c r="AL15"/>
-      <c r="AM15"/>
+      <c r="AM15" t="n">
+        <v>0.0522665714285714</v>
+      </c>
       <c r="AN15"/>
       <c r="AO15"/>
       <c r="AP15"/>
@@ -2243,13 +2243,13 @@
       <c r="AZ15"/>
       <c r="BA15"/>
       <c r="BB15"/>
-      <c r="BC15" t="n">
-        <v>85.7142857142857</v>
-      </c>
+      <c r="BC15"/>
       <c r="BD15"/>
       <c r="BE15"/>
       <c r="BF15"/>
-      <c r="BG15"/>
+      <c r="BG15" t="n">
+        <v>85.7142857142857</v>
+      </c>
       <c r="BH15"/>
       <c r="BI15"/>
       <c r="BJ15"/>
@@ -2264,22 +2264,22 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C16" t="n">
-        <v>1.14285714285714</v>
+        <v>1.28571428571429</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0529387142857143</v>
+        <v>0.0535224285714286</v>
       </c>
       <c r="E16" t="n">
-        <v>85.7142857142857</v>
+        <v>71.4285714285714</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
         <v>79</v>
@@ -2288,7 +2288,7 @@
         <v>73</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>7</v>
@@ -2298,13 +2298,13 @@
       <c r="M16"/>
       <c r="N16"/>
       <c r="O16"/>
-      <c r="P16"/>
+      <c r="P16" t="n">
+        <v>1.28571428571429</v>
+      </c>
       <c r="Q16"/>
       <c r="R16"/>
       <c r="S16"/>
-      <c r="T16" t="n">
-        <v>1.14285714285714</v>
-      </c>
+      <c r="T16"/>
       <c r="U16"/>
       <c r="V16"/>
       <c r="W16"/>
@@ -2320,13 +2320,13 @@
       <c r="AG16"/>
       <c r="AH16"/>
       <c r="AI16"/>
-      <c r="AJ16"/>
+      <c r="AJ16" t="n">
+        <v>0.0535224285714286</v>
+      </c>
       <c r="AK16"/>
       <c r="AL16"/>
       <c r="AM16"/>
-      <c r="AN16" t="n">
-        <v>0.0529387142857143</v>
-      </c>
+      <c r="AN16"/>
       <c r="AO16"/>
       <c r="AP16"/>
       <c r="AQ16"/>
@@ -2342,13 +2342,13 @@
       <c r="BA16"/>
       <c r="BB16"/>
       <c r="BC16"/>
-      <c r="BD16"/>
+      <c r="BD16" t="n">
+        <v>71.4285714285714</v>
+      </c>
       <c r="BE16"/>
       <c r="BF16"/>
       <c r="BG16"/>
-      <c r="BH16" t="n">
-        <v>85.7142857142857</v>
-      </c>
+      <c r="BH16"/>
       <c r="BI16"/>
       <c r="BJ16"/>
       <c r="BK16"/>
@@ -2362,22 +2362,22 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C17" t="n">
         <v>1.28571428571429</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0535224285714286</v>
+        <v>0.0529387142857143</v>
       </c>
       <c r="E17" t="n">
         <v>71.4285714285714</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
         <v>79</v>
@@ -2396,13 +2396,13 @@
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17"/>
-      <c r="P17" t="n">
-        <v>1.28571428571429</v>
-      </c>
+      <c r="P17"/>
       <c r="Q17"/>
       <c r="R17"/>
       <c r="S17"/>
-      <c r="T17"/>
+      <c r="T17" t="n">
+        <v>1.28571428571429</v>
+      </c>
       <c r="U17"/>
       <c r="V17"/>
       <c r="W17"/>
@@ -2418,13 +2418,13 @@
       <c r="AG17"/>
       <c r="AH17"/>
       <c r="AI17"/>
-      <c r="AJ17" t="n">
-        <v>0.0535224285714286</v>
-      </c>
+      <c r="AJ17"/>
       <c r="AK17"/>
       <c r="AL17"/>
       <c r="AM17"/>
-      <c r="AN17"/>
+      <c r="AN17" t="n">
+        <v>0.0529387142857143</v>
+      </c>
       <c r="AO17"/>
       <c r="AP17"/>
       <c r="AQ17"/>
@@ -2440,13 +2440,13 @@
       <c r="BA17"/>
       <c r="BB17"/>
       <c r="BC17"/>
-      <c r="BD17" t="n">
-        <v>71.4285714285714</v>
-      </c>
+      <c r="BD17"/>
       <c r="BE17"/>
       <c r="BF17"/>
       <c r="BG17"/>
-      <c r="BH17"/>
+      <c r="BH17" t="n">
+        <v>71.4285714285714</v>
+      </c>
       <c r="BI17"/>
       <c r="BJ17"/>
       <c r="BK17"/>
@@ -3244,22 +3244,22 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C26" t="n">
         <v>1.71428571428571</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0533125714285714</v>
+        <v>0.0540902857142857</v>
       </c>
       <c r="E26" t="n">
         <v>28.5714285714286</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
         <v>79</v>
@@ -3278,13 +3278,13 @@
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26"/>
-      <c r="P26" t="n">
-        <v>1.71428571428571</v>
-      </c>
+      <c r="P26"/>
       <c r="Q26"/>
       <c r="R26"/>
       <c r="S26"/>
-      <c r="T26"/>
+      <c r="T26" t="n">
+        <v>1.71428571428571</v>
+      </c>
       <c r="U26"/>
       <c r="V26"/>
       <c r="W26"/>
@@ -3300,13 +3300,13 @@
       <c r="AG26"/>
       <c r="AH26"/>
       <c r="AI26"/>
-      <c r="AJ26" t="n">
-        <v>0.0533125714285714</v>
-      </c>
+      <c r="AJ26"/>
       <c r="AK26"/>
       <c r="AL26"/>
       <c r="AM26"/>
-      <c r="AN26"/>
+      <c r="AN26" t="n">
+        <v>0.0540902857142857</v>
+      </c>
       <c r="AO26"/>
       <c r="AP26"/>
       <c r="AQ26"/>
@@ -3322,13 +3322,13 @@
       <c r="BA26"/>
       <c r="BB26"/>
       <c r="BC26"/>
-      <c r="BD26" t="n">
-        <v>28.5714285714286</v>
-      </c>
+      <c r="BD26"/>
       <c r="BE26"/>
       <c r="BF26"/>
       <c r="BG26"/>
-      <c r="BH26"/>
+      <c r="BH26" t="n">
+        <v>28.5714285714286</v>
+      </c>
       <c r="BI26"/>
       <c r="BJ26"/>
       <c r="BK26"/>
@@ -3342,22 +3342,22 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C27" t="n">
-        <v>1.85714285714286</v>
+        <v>1.71428571428571</v>
       </c>
       <c r="D27" t="n">
-        <v>0.055479</v>
+        <v>0.0533125714285714</v>
       </c>
       <c r="E27" t="n">
-        <v>14.2857142857143</v>
+        <v>28.5714285714286</v>
       </c>
       <c r="F27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
         <v>79</v>
@@ -3366,19 +3366,19 @@
         <v>73</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
       </c>
       <c r="K27"/>
-      <c r="L27" t="n">
-        <v>1.85714285714286</v>
-      </c>
+      <c r="L27"/>
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27"/>
-      <c r="P27"/>
+      <c r="P27" t="n">
+        <v>1.71428571428571</v>
+      </c>
       <c r="Q27"/>
       <c r="R27"/>
       <c r="S27"/>
@@ -3394,13 +3394,13 @@
       <c r="AC27"/>
       <c r="AD27"/>
       <c r="AE27"/>
-      <c r="AF27" t="n">
-        <v>0.055479</v>
-      </c>
+      <c r="AF27"/>
       <c r="AG27"/>
       <c r="AH27"/>
       <c r="AI27"/>
-      <c r="AJ27"/>
+      <c r="AJ27" t="n">
+        <v>0.0533125714285714</v>
+      </c>
       <c r="AK27"/>
       <c r="AL27"/>
       <c r="AM27"/>
@@ -3416,13 +3416,13 @@
       <c r="AW27"/>
       <c r="AX27"/>
       <c r="AY27"/>
-      <c r="AZ27" t="n">
-        <v>14.2857142857143</v>
-      </c>
+      <c r="AZ27"/>
       <c r="BA27"/>
       <c r="BB27"/>
       <c r="BC27"/>
-      <c r="BD27"/>
+      <c r="BD27" t="n">
+        <v>28.5714285714286</v>
+      </c>
       <c r="BE27"/>
       <c r="BF27"/>
       <c r="BG27"/>
@@ -3449,19 +3449,19 @@
         <v>1.85714285714286</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0541118571428571</v>
+        <v>0.055479</v>
       </c>
       <c r="E28" t="n">
         <v>14.2857142857143</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G28" t="s">
         <v>79</v>
       </c>
       <c r="H28" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -3470,12 +3470,12 @@
         <v>7</v>
       </c>
       <c r="K28"/>
-      <c r="L28"/>
+      <c r="L28" t="n">
+        <v>1.85714285714286</v>
+      </c>
       <c r="M28"/>
       <c r="N28"/>
-      <c r="O28" t="n">
-        <v>1.85714285714286</v>
-      </c>
+      <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
       <c r="R28"/>
@@ -3492,12 +3492,12 @@
       <c r="AC28"/>
       <c r="AD28"/>
       <c r="AE28"/>
-      <c r="AF28"/>
+      <c r="AF28" t="n">
+        <v>0.055479</v>
+      </c>
       <c r="AG28"/>
       <c r="AH28"/>
-      <c r="AI28" t="n">
-        <v>0.0541118571428571</v>
-      </c>
+      <c r="AI28"/>
       <c r="AJ28"/>
       <c r="AK28"/>
       <c r="AL28"/>
@@ -3514,12 +3514,12 @@
       <c r="AW28"/>
       <c r="AX28"/>
       <c r="AY28"/>
-      <c r="AZ28"/>
+      <c r="AZ28" t="n">
+        <v>14.2857142857143</v>
+      </c>
       <c r="BA28"/>
       <c r="BB28"/>
-      <c r="BC28" t="n">
-        <v>14.2857142857143</v>
-      </c>
+      <c r="BC28"/>
       <c r="BD28"/>
       <c r="BE28"/>
       <c r="BF28"/>
@@ -3547,19 +3547,19 @@
         <v>1.85714285714286</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0549114285714286</v>
+        <v>0.0541118571428571</v>
       </c>
       <c r="E29" t="n">
         <v>14.2857142857143</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
         <v>79</v>
       </c>
       <c r="H29" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -3571,14 +3571,14 @@
       <c r="L29"/>
       <c r="M29"/>
       <c r="N29"/>
-      <c r="O29"/>
+      <c r="O29" t="n">
+        <v>1.85714285714286</v>
+      </c>
       <c r="P29"/>
       <c r="Q29"/>
       <c r="R29"/>
       <c r="S29"/>
-      <c r="T29" t="n">
-        <v>1.85714285714286</v>
-      </c>
+      <c r="T29"/>
       <c r="U29"/>
       <c r="V29"/>
       <c r="W29"/>
@@ -3593,14 +3593,14 @@
       <c r="AF29"/>
       <c r="AG29"/>
       <c r="AH29"/>
-      <c r="AI29"/>
+      <c r="AI29" t="n">
+        <v>0.0541118571428571</v>
+      </c>
       <c r="AJ29"/>
       <c r="AK29"/>
       <c r="AL29"/>
       <c r="AM29"/>
-      <c r="AN29" t="n">
-        <v>0.0549114285714286</v>
-      </c>
+      <c r="AN29"/>
       <c r="AO29"/>
       <c r="AP29"/>
       <c r="AQ29"/>
@@ -3615,14 +3615,14 @@
       <c r="AZ29"/>
       <c r="BA29"/>
       <c r="BB29"/>
-      <c r="BC29"/>
+      <c r="BC29" t="n">
+        <v>14.2857142857143</v>
+      </c>
       <c r="BD29"/>
       <c r="BE29"/>
       <c r="BF29"/>
       <c r="BG29"/>
-      <c r="BH29" t="n">
-        <v>14.2857142857143</v>
-      </c>
+      <c r="BH29"/>
       <c r="BI29"/>
       <c r="BJ29"/>
       <c r="BK29"/>
@@ -3642,16 +3642,16 @@
         <v>70</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1.85714285714286</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0561408571428571</v>
+        <v>0.0547512857142857</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>14.2857142857143</v>
       </c>
       <c r="F30" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
         <v>79</v>
@@ -3660,14 +3660,12 @@
         <v>80</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>7</v>
       </c>
-      <c r="K30" t="n">
-        <v>2</v>
-      </c>
+      <c r="K30"/>
       <c r="L30"/>
       <c r="M30"/>
       <c r="N30"/>
@@ -3675,7 +3673,9 @@
       <c r="P30"/>
       <c r="Q30"/>
       <c r="R30"/>
-      <c r="S30"/>
+      <c r="S30" t="n">
+        <v>1.85714285714286</v>
+      </c>
       <c r="T30"/>
       <c r="U30"/>
       <c r="V30"/>
@@ -3687,9 +3687,7 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30"/>
-      <c r="AE30" t="n">
-        <v>0.0561408571428571</v>
-      </c>
+      <c r="AE30"/>
       <c r="AF30"/>
       <c r="AG30"/>
       <c r="AH30"/>
@@ -3697,7 +3695,9 @@
       <c r="AJ30"/>
       <c r="AK30"/>
       <c r="AL30"/>
-      <c r="AM30"/>
+      <c r="AM30" t="n">
+        <v>0.0547512857142857</v>
+      </c>
       <c r="AN30"/>
       <c r="AO30"/>
       <c r="AP30"/>
@@ -3709,9 +3709,7 @@
       <c r="AV30"/>
       <c r="AW30"/>
       <c r="AX30"/>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
+      <c r="AY30"/>
       <c r="AZ30"/>
       <c r="BA30"/>
       <c r="BB30"/>
@@ -3719,7 +3717,9 @@
       <c r="BD30"/>
       <c r="BE30"/>
       <c r="BF30"/>
-      <c r="BG30"/>
+      <c r="BG30" t="n">
+        <v>14.2857142857143</v>
+      </c>
       <c r="BH30"/>
       <c r="BI30"/>
       <c r="BJ30"/>
@@ -3743,13 +3743,13 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0556252857142857</v>
+        <v>0.0561408571428571</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G31" t="s">
         <v>79</v>
@@ -3763,7 +3763,9 @@
       <c r="J31" t="n">
         <v>7</v>
       </c>
-      <c r="K31"/>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
       <c r="L31"/>
       <c r="M31"/>
       <c r="N31"/>
@@ -3771,9 +3773,7 @@
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31"/>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
+      <c r="S31"/>
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31"/>
@@ -3785,7 +3785,9 @@
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31"/>
-      <c r="AE31"/>
+      <c r="AE31" t="n">
+        <v>0.0561408571428571</v>
+      </c>
       <c r="AF31"/>
       <c r="AG31"/>
       <c r="AH31"/>
@@ -3793,9 +3795,7 @@
       <c r="AJ31"/>
       <c r="AK31"/>
       <c r="AL31"/>
-      <c r="AM31" t="n">
-        <v>0.0556252857142857</v>
-      </c>
+      <c r="AM31"/>
       <c r="AN31"/>
       <c r="AO31"/>
       <c r="AP31"/>
@@ -3807,7 +3807,9 @@
       <c r="AV31"/>
       <c r="AW31"/>
       <c r="AX31"/>
-      <c r="AY31"/>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ31"/>
       <c r="BA31"/>
       <c r="BB31"/>
@@ -3815,9 +3817,7 @@
       <c r="BD31"/>
       <c r="BE31"/>
       <c r="BF31"/>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG31"/>
       <c r="BH31"/>
       <c r="BI31"/>
       <c r="BJ31"/>
@@ -8542,10 +8542,10 @@
         <v>81</v>
       </c>
       <c r="C80" t="n">
-        <v>4.28571428571429</v>
+        <v>4.14285714285714</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0836104285714286</v>
+        <v>0.0815444285714286</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -8574,7 +8574,7 @@
       <c r="Q80"/>
       <c r="R80"/>
       <c r="S80" t="n">
-        <v>4.28571428571429</v>
+        <v>4.14285714285714</v>
       </c>
       <c r="T80"/>
       <c r="U80"/>
@@ -8596,7 +8596,7 @@
       <c r="AK80"/>
       <c r="AL80"/>
       <c r="AM80" t="n">
-        <v>0.0836104285714286</v>
+        <v>0.0815444285714286</v>
       </c>
       <c r="AN80"/>
       <c r="AO80"/>
@@ -8640,10 +8640,10 @@
         <v>81</v>
       </c>
       <c r="C81" t="n">
-        <v>4.28571428571429</v>
+        <v>4.14285714285714</v>
       </c>
       <c r="D81" t="n">
-        <v>0.078446</v>
+        <v>0.0765948571428571</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
       <c r="R81"/>
       <c r="S81"/>
       <c r="T81" t="n">
-        <v>4.28571428571429</v>
+        <v>4.14285714285714</v>
       </c>
       <c r="U81"/>
       <c r="V81"/>
@@ -8695,7 +8695,7 @@
       <c r="AL81"/>
       <c r="AM81"/>
       <c r="AN81" t="n">
-        <v>0.078446</v>
+        <v>0.0765948571428571</v>
       </c>
       <c r="AO81"/>
       <c r="AP81"/>
@@ -8741,7 +8741,7 @@
         <v>4.85714285714286</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0860757142857143</v>
+        <v>0.826023142857143</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -8750,10 +8750,10 @@
         <v>75</v>
       </c>
       <c r="G82" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H82" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -8770,10 +8770,10 @@
       <c r="Q82"/>
       <c r="R82"/>
       <c r="S82"/>
-      <c r="T82" t="n">
+      <c r="T82"/>
+      <c r="U82" t="n">
         <v>4.85714285714286</v>
       </c>
-      <c r="U82"/>
       <c r="V82"/>
       <c r="W82"/>
       <c r="X82"/>
@@ -8792,10 +8792,10 @@
       <c r="AK82"/>
       <c r="AL82"/>
       <c r="AM82"/>
-      <c r="AN82" t="n">
-        <v>0.0860757142857143</v>
-      </c>
-      <c r="AO82"/>
+      <c r="AN82"/>
+      <c r="AO82" t="n">
+        <v>0.826023142857143</v>
+      </c>
       <c r="AP82"/>
       <c r="AQ82"/>
       <c r="AR82"/>
@@ -8814,10 +8814,10 @@
       <c r="BE82"/>
       <c r="BF82"/>
       <c r="BG82"/>
-      <c r="BH82" t="n">
+      <c r="BH82"/>
+      <c r="BI82" t="n">
         <v>0</v>
       </c>
-      <c r="BI82"/>
       <c r="BJ82"/>
       <c r="BK82"/>
       <c r="BL82"/>
@@ -8839,7 +8839,7 @@
         <v>4.85714285714286</v>
       </c>
       <c r="D83" t="n">
-        <v>0.826023142857143</v>
+        <v>0.705355</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
         <v>72</v>
       </c>
       <c r="H83" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -8869,10 +8869,10 @@
       <c r="R83"/>
       <c r="S83"/>
       <c r="T83"/>
-      <c r="U83" t="n">
+      <c r="U83"/>
+      <c r="V83" t="n">
         <v>4.85714285714286</v>
       </c>
-      <c r="V83"/>
       <c r="W83"/>
       <c r="X83"/>
       <c r="Y83"/>
@@ -8891,10 +8891,10 @@
       <c r="AL83"/>
       <c r="AM83"/>
       <c r="AN83"/>
-      <c r="AO83" t="n">
-        <v>0.826023142857143</v>
-      </c>
-      <c r="AP83"/>
+      <c r="AO83"/>
+      <c r="AP83" t="n">
+        <v>0.705355</v>
+      </c>
       <c r="AQ83"/>
       <c r="AR83"/>
       <c r="AS83"/>
@@ -8913,10 +8913,10 @@
       <c r="BF83"/>
       <c r="BG83"/>
       <c r="BH83"/>
-      <c r="BI83" t="n">
+      <c r="BI83"/>
+      <c r="BJ83" t="n">
         <v>0</v>
       </c>
-      <c r="BJ83"/>
       <c r="BK83"/>
       <c r="BL83"/>
       <c r="BM83"/>
@@ -8934,19 +8934,19 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>4.85714285714286</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>0.705355</v>
+        <v>0.0850145714285714</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G84" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s">
         <v>73</v>
@@ -8958,7 +8958,9 @@
         <v>7</v>
       </c>
       <c r="K84"/>
-      <c r="L84"/>
+      <c r="L84" t="n">
+        <v>5</v>
+      </c>
       <c r="M84"/>
       <c r="N84"/>
       <c r="O84"/>
@@ -8968,9 +8970,7 @@
       <c r="S84"/>
       <c r="T84"/>
       <c r="U84"/>
-      <c r="V84" t="n">
-        <v>4.85714285714286</v>
-      </c>
+      <c r="V84"/>
       <c r="W84"/>
       <c r="X84"/>
       <c r="Y84"/>
@@ -8980,7 +8980,9 @@
       <c r="AC84"/>
       <c r="AD84"/>
       <c r="AE84"/>
-      <c r="AF84"/>
+      <c r="AF84" t="n">
+        <v>0.0850145714285714</v>
+      </c>
       <c r="AG84"/>
       <c r="AH84"/>
       <c r="AI84"/>
@@ -8990,9 +8992,7 @@
       <c r="AM84"/>
       <c r="AN84"/>
       <c r="AO84"/>
-      <c r="AP84" t="n">
-        <v>0.705355</v>
-      </c>
+      <c r="AP84"/>
       <c r="AQ84"/>
       <c r="AR84"/>
       <c r="AS84"/>
@@ -9002,7 +9002,9 @@
       <c r="AW84"/>
       <c r="AX84"/>
       <c r="AY84"/>
-      <c r="AZ84"/>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
       <c r="BA84"/>
       <c r="BB84"/>
       <c r="BC84"/>
@@ -9012,9 +9014,7 @@
       <c r="BG84"/>
       <c r="BH84"/>
       <c r="BI84"/>
-      <c r="BJ84" t="n">
-        <v>0</v>
-      </c>
+      <c r="BJ84"/>
       <c r="BK84"/>
       <c r="BL84"/>
       <c r="BM84"/>
@@ -9035,7 +9035,7 @@
         <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0850145714285714</v>
+        <v>0.811395142857143</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>71</v>
       </c>
       <c r="G85" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H85" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -9056,10 +9056,10 @@
         <v>7</v>
       </c>
       <c r="K85"/>
-      <c r="L85" t="n">
+      <c r="L85"/>
+      <c r="M85" t="n">
         <v>5</v>
       </c>
-      <c r="M85"/>
       <c r="N85"/>
       <c r="O85"/>
       <c r="P85"/>
@@ -9078,10 +9078,10 @@
       <c r="AC85"/>
       <c r="AD85"/>
       <c r="AE85"/>
-      <c r="AF85" t="n">
-        <v>0.0850145714285714</v>
-      </c>
-      <c r="AG85"/>
+      <c r="AF85"/>
+      <c r="AG85" t="n">
+        <v>0.811395142857143</v>
+      </c>
       <c r="AH85"/>
       <c r="AI85"/>
       <c r="AJ85"/>
@@ -9100,10 +9100,10 @@
       <c r="AW85"/>
       <c r="AX85"/>
       <c r="AY85"/>
-      <c r="AZ85" t="n">
+      <c r="AZ85"/>
+      <c r="BA85" t="n">
         <v>0</v>
       </c>
-      <c r="BA85"/>
       <c r="BB85"/>
       <c r="BC85"/>
       <c r="BD85"/>
@@ -9133,7 +9133,7 @@
         <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>0.811395142857143</v>
+        <v>0.694516428571429</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -9145,7 +9145,7 @@
         <v>72</v>
       </c>
       <c r="H86" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -9155,10 +9155,10 @@
       </c>
       <c r="K86"/>
       <c r="L86"/>
-      <c r="M86" t="n">
+      <c r="M86"/>
+      <c r="N86" t="n">
         <v>5</v>
       </c>
-      <c r="N86"/>
       <c r="O86"/>
       <c r="P86"/>
       <c r="Q86"/>
@@ -9177,10 +9177,10 @@
       <c r="AD86"/>
       <c r="AE86"/>
       <c r="AF86"/>
-      <c r="AG86" t="n">
-        <v>0.811395142857143</v>
-      </c>
-      <c r="AH86"/>
+      <c r="AG86"/>
+      <c r="AH86" t="n">
+        <v>0.694516428571429</v>
+      </c>
       <c r="AI86"/>
       <c r="AJ86"/>
       <c r="AK86"/>
@@ -9199,10 +9199,10 @@
       <c r="AX86"/>
       <c r="AY86"/>
       <c r="AZ86"/>
-      <c r="BA86" t="n">
+      <c r="BA86"/>
+      <c r="BB86" t="n">
         <v>0</v>
       </c>
-      <c r="BB86"/>
       <c r="BC86"/>
       <c r="BD86"/>
       <c r="BE86"/>
@@ -9231,19 +9231,19 @@
         <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>0.694516428571429</v>
+        <v>0.0794437142857143</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G87" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -9254,10 +9254,10 @@
       <c r="K87"/>
       <c r="L87"/>
       <c r="M87"/>
-      <c r="N87" t="n">
+      <c r="N87"/>
+      <c r="O87" t="n">
         <v>5</v>
       </c>
-      <c r="O87"/>
       <c r="P87"/>
       <c r="Q87"/>
       <c r="R87"/>
@@ -9276,10 +9276,10 @@
       <c r="AE87"/>
       <c r="AF87"/>
       <c r="AG87"/>
-      <c r="AH87" t="n">
-        <v>0.694516428571429</v>
-      </c>
-      <c r="AI87"/>
+      <c r="AH87"/>
+      <c r="AI87" t="n">
+        <v>0.0794437142857143</v>
+      </c>
       <c r="AJ87"/>
       <c r="AK87"/>
       <c r="AL87"/>
@@ -9298,10 +9298,10 @@
       <c r="AY87"/>
       <c r="AZ87"/>
       <c r="BA87"/>
-      <c r="BB87" t="n">
+      <c r="BB87"/>
+      <c r="BC87" t="n">
         <v>0</v>
       </c>
-      <c r="BC87"/>
       <c r="BD87"/>
       <c r="BE87"/>
       <c r="BF87"/>
@@ -9329,7 +9329,7 @@
         <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0794437142857143</v>
+        <v>0.0761128571428571</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -9341,7 +9341,7 @@
         <v>79</v>
       </c>
       <c r="H88" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -9353,10 +9353,10 @@
       <c r="L88"/>
       <c r="M88"/>
       <c r="N88"/>
-      <c r="O88" t="n">
+      <c r="O88"/>
+      <c r="P88" t="n">
         <v>5</v>
       </c>
-      <c r="P88"/>
       <c r="Q88"/>
       <c r="R88"/>
       <c r="S88"/>
@@ -9375,10 +9375,10 @@
       <c r="AF88"/>
       <c r="AG88"/>
       <c r="AH88"/>
-      <c r="AI88" t="n">
-        <v>0.0794437142857143</v>
-      </c>
-      <c r="AJ88"/>
+      <c r="AI88"/>
+      <c r="AJ88" t="n">
+        <v>0.0761128571428571</v>
+      </c>
       <c r="AK88"/>
       <c r="AL88"/>
       <c r="AM88"/>
@@ -9397,10 +9397,10 @@
       <c r="AZ88"/>
       <c r="BA88"/>
       <c r="BB88"/>
-      <c r="BC88" t="n">
+      <c r="BC88"/>
+      <c r="BD88" t="n">
         <v>0</v>
       </c>
-      <c r="BD88"/>
       <c r="BE88"/>
       <c r="BF88"/>
       <c r="BG88"/>
@@ -9427,7 +9427,7 @@
         <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0761128571428571</v>
+        <v>0.7128</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -9436,10 +9436,10 @@
         <v>74</v>
       </c>
       <c r="G89" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H89" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -9452,10 +9452,10 @@
       <c r="M89"/>
       <c r="N89"/>
       <c r="O89"/>
-      <c r="P89" t="n">
+      <c r="P89"/>
+      <c r="Q89" t="n">
         <v>5</v>
       </c>
-      <c r="Q89"/>
       <c r="R89"/>
       <c r="S89"/>
       <c r="T89"/>
@@ -9474,10 +9474,10 @@
       <c r="AG89"/>
       <c r="AH89"/>
       <c r="AI89"/>
-      <c r="AJ89" t="n">
-        <v>0.0761128571428571</v>
-      </c>
-      <c r="AK89"/>
+      <c r="AJ89"/>
+      <c r="AK89" t="n">
+        <v>0.7128</v>
+      </c>
       <c r="AL89"/>
       <c r="AM89"/>
       <c r="AN89"/>
@@ -9496,10 +9496,10 @@
       <c r="BA89"/>
       <c r="BB89"/>
       <c r="BC89"/>
-      <c r="BD89" t="n">
+      <c r="BD89"/>
+      <c r="BE89" t="n">
         <v>0</v>
       </c>
-      <c r="BE89"/>
       <c r="BF89"/>
       <c r="BG89"/>
       <c r="BH89"/>
@@ -9525,7 +9525,7 @@
         <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>0.7128</v>
+        <v>0.635485428571429</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
         <v>72</v>
       </c>
       <c r="H90" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -9551,10 +9551,10 @@
       <c r="N90"/>
       <c r="O90"/>
       <c r="P90"/>
-      <c r="Q90" t="n">
+      <c r="Q90"/>
+      <c r="R90" t="n">
         <v>5</v>
       </c>
-      <c r="R90"/>
       <c r="S90"/>
       <c r="T90"/>
       <c r="U90"/>
@@ -9573,10 +9573,10 @@
       <c r="AH90"/>
       <c r="AI90"/>
       <c r="AJ90"/>
-      <c r="AK90" t="n">
-        <v>0.7128</v>
-      </c>
-      <c r="AL90"/>
+      <c r="AK90"/>
+      <c r="AL90" t="n">
+        <v>0.635485428571429</v>
+      </c>
       <c r="AM90"/>
       <c r="AN90"/>
       <c r="AO90"/>
@@ -9595,10 +9595,10 @@
       <c r="BB90"/>
       <c r="BC90"/>
       <c r="BD90"/>
-      <c r="BE90" t="n">
+      <c r="BE90"/>
+      <c r="BF90" t="n">
         <v>0</v>
       </c>
-      <c r="BF90"/>
       <c r="BG90"/>
       <c r="BH90"/>
       <c r="BI90"/>
@@ -9623,19 +9623,19 @@
         <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>0.635485428571429</v>
+        <v>0.0787695714285714</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -9650,14 +9650,14 @@
       <c r="O91"/>
       <c r="P91"/>
       <c r="Q91"/>
-      <c r="R91" t="n">
-        <v>5</v>
-      </c>
+      <c r="R91"/>
       <c r="S91"/>
       <c r="T91"/>
       <c r="U91"/>
       <c r="V91"/>
-      <c r="W91"/>
+      <c r="W91" t="n">
+        <v>5</v>
+      </c>
       <c r="X91"/>
       <c r="Y91"/>
       <c r="Z91"/>
@@ -9672,14 +9672,14 @@
       <c r="AI91"/>
       <c r="AJ91"/>
       <c r="AK91"/>
-      <c r="AL91" t="n">
-        <v>0.635485428571429</v>
-      </c>
+      <c r="AL91"/>
       <c r="AM91"/>
       <c r="AN91"/>
       <c r="AO91"/>
       <c r="AP91"/>
-      <c r="AQ91"/>
+      <c r="AQ91" t="n">
+        <v>0.0787695714285714</v>
+      </c>
       <c r="AR91"/>
       <c r="AS91"/>
       <c r="AT91"/>
@@ -9694,14 +9694,14 @@
       <c r="BC91"/>
       <c r="BD91"/>
       <c r="BE91"/>
-      <c r="BF91" t="n">
-        <v>0</v>
-      </c>
+      <c r="BF91"/>
       <c r="BG91"/>
       <c r="BH91"/>
       <c r="BI91"/>
       <c r="BJ91"/>
-      <c r="BK91"/>
+      <c r="BK91" t="n">
+        <v>0</v>
+      </c>
       <c r="BL91"/>
       <c r="BM91"/>
       <c r="BN91"/>
@@ -9721,19 +9721,19 @@
         <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0916192857142857</v>
+        <v>0.0755504285714286</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G92" t="s">
         <v>79</v>
       </c>
       <c r="H92" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -9749,14 +9749,14 @@
       <c r="P92"/>
       <c r="Q92"/>
       <c r="R92"/>
-      <c r="S92" t="n">
-        <v>5</v>
-      </c>
+      <c r="S92"/>
       <c r="T92"/>
       <c r="U92"/>
       <c r="V92"/>
       <c r="W92"/>
-      <c r="X92"/>
+      <c r="X92" t="n">
+        <v>5</v>
+      </c>
       <c r="Y92"/>
       <c r="Z92"/>
       <c r="AA92"/>
@@ -9771,14 +9771,14 @@
       <c r="AJ92"/>
       <c r="AK92"/>
       <c r="AL92"/>
-      <c r="AM92" t="n">
-        <v>0.0916192857142857</v>
-      </c>
+      <c r="AM92"/>
       <c r="AN92"/>
       <c r="AO92"/>
       <c r="AP92"/>
       <c r="AQ92"/>
-      <c r="AR92"/>
+      <c r="AR92" t="n">
+        <v>0.0755504285714286</v>
+      </c>
       <c r="AS92"/>
       <c r="AT92"/>
       <c r="AU92"/>
@@ -9793,14 +9793,14 @@
       <c r="BD92"/>
       <c r="BE92"/>
       <c r="BF92"/>
-      <c r="BG92" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG92"/>
       <c r="BH92"/>
       <c r="BI92"/>
       <c r="BJ92"/>
       <c r="BK92"/>
-      <c r="BL92"/>
+      <c r="BL92" t="n">
+        <v>0</v>
+      </c>
       <c r="BM92"/>
       <c r="BN92"/>
       <c r="BO92"/>
@@ -9819,7 +9819,7 @@
         <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0787695714285714</v>
+        <v>0.703970714285714</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -9828,7 +9828,7 @@
         <v>76</v>
       </c>
       <c r="G93" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H93" t="s">
         <v>80</v>
@@ -9851,11 +9851,11 @@
       <c r="T93"/>
       <c r="U93"/>
       <c r="V93"/>
-      <c r="W93" t="n">
+      <c r="W93"/>
+      <c r="X93"/>
+      <c r="Y93" t="n">
         <v>5</v>
       </c>
-      <c r="X93"/>
-      <c r="Y93"/>
       <c r="Z93"/>
       <c r="AA93"/>
       <c r="AB93"/>
@@ -9873,11 +9873,11 @@
       <c r="AN93"/>
       <c r="AO93"/>
       <c r="AP93"/>
-      <c r="AQ93" t="n">
-        <v>0.0787695714285714</v>
-      </c>
+      <c r="AQ93"/>
       <c r="AR93"/>
-      <c r="AS93"/>
+      <c r="AS93" t="n">
+        <v>0.703970714285714</v>
+      </c>
       <c r="AT93"/>
       <c r="AU93"/>
       <c r="AV93"/>
@@ -9895,11 +9895,11 @@
       <c r="BH93"/>
       <c r="BI93"/>
       <c r="BJ93"/>
-      <c r="BK93" t="n">
+      <c r="BK93"/>
+      <c r="BL93"/>
+      <c r="BM93" t="n">
         <v>0</v>
       </c>
-      <c r="BL93"/>
-      <c r="BM93"/>
       <c r="BN93"/>
       <c r="BO93"/>
       <c r="BP93"/>
@@ -9917,7 +9917,7 @@
         <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0755504285714286</v>
+        <v>0.629823142857143</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         <v>76</v>
       </c>
       <c r="G94" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H94" t="s">
         <v>73</v>
@@ -9950,11 +9950,11 @@
       <c r="U94"/>
       <c r="V94"/>
       <c r="W94"/>
-      <c r="X94" t="n">
+      <c r="X94"/>
+      <c r="Y94"/>
+      <c r="Z94" t="n">
         <v>5</v>
       </c>
-      <c r="Y94"/>
-      <c r="Z94"/>
       <c r="AA94"/>
       <c r="AB94"/>
       <c r="AC94"/>
@@ -9972,11 +9972,11 @@
       <c r="AO94"/>
       <c r="AP94"/>
       <c r="AQ94"/>
-      <c r="AR94" t="n">
-        <v>0.0755504285714286</v>
-      </c>
+      <c r="AR94"/>
       <c r="AS94"/>
-      <c r="AT94"/>
+      <c r="AT94" t="n">
+        <v>0.629823142857143</v>
+      </c>
       <c r="AU94"/>
       <c r="AV94"/>
       <c r="AW94"/>
@@ -9994,11 +9994,11 @@
       <c r="BI94"/>
       <c r="BJ94"/>
       <c r="BK94"/>
-      <c r="BL94" t="n">
+      <c r="BL94"/>
+      <c r="BM94"/>
+      <c r="BN94" t="n">
         <v>0</v>
       </c>
-      <c r="BM94"/>
-      <c r="BN94"/>
       <c r="BO94"/>
       <c r="BP94"/>
       <c r="BQ94"/>
@@ -10015,16 +10015,16 @@
         <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>0.703970714285714</v>
+        <v>0.0786617142857143</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G95" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s">
         <v>80</v>
@@ -10049,11 +10049,11 @@
       <c r="V95"/>
       <c r="W95"/>
       <c r="X95"/>
-      <c r="Y95" t="n">
+      <c r="Y95"/>
+      <c r="Z95"/>
+      <c r="AA95" t="n">
         <v>5</v>
       </c>
-      <c r="Z95"/>
-      <c r="AA95"/>
       <c r="AB95"/>
       <c r="AC95"/>
       <c r="AD95"/>
@@ -10071,11 +10071,11 @@
       <c r="AP95"/>
       <c r="AQ95"/>
       <c r="AR95"/>
-      <c r="AS95" t="n">
-        <v>0.703970714285714</v>
-      </c>
+      <c r="AS95"/>
       <c r="AT95"/>
-      <c r="AU95"/>
+      <c r="AU95" t="n">
+        <v>0.0786617142857143</v>
+      </c>
       <c r="AV95"/>
       <c r="AW95"/>
       <c r="AX95"/>
@@ -10093,11 +10093,11 @@
       <c r="BJ95"/>
       <c r="BK95"/>
       <c r="BL95"/>
-      <c r="BM95" t="n">
+      <c r="BM95"/>
+      <c r="BN95"/>
+      <c r="BO95" t="n">
         <v>0</v>
       </c>
-      <c r="BN95"/>
-      <c r="BO95"/>
       <c r="BP95"/>
       <c r="BQ95"/>
       <c r="BR95"/>
@@ -10113,16 +10113,16 @@
         <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>0.629823142857143</v>
+        <v>0.0754587142857143</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H96" t="s">
         <v>73</v>
@@ -10148,11 +10148,11 @@
       <c r="W96"/>
       <c r="X96"/>
       <c r="Y96"/>
-      <c r="Z96" t="n">
+      <c r="Z96"/>
+      <c r="AA96"/>
+      <c r="AB96" t="n">
         <v>5</v>
       </c>
-      <c r="AA96"/>
-      <c r="AB96"/>
       <c r="AC96"/>
       <c r="AD96"/>
       <c r="AE96"/>
@@ -10170,11 +10170,11 @@
       <c r="AQ96"/>
       <c r="AR96"/>
       <c r="AS96"/>
-      <c r="AT96" t="n">
-        <v>0.629823142857143</v>
-      </c>
+      <c r="AT96"/>
       <c r="AU96"/>
-      <c r="AV96"/>
+      <c r="AV96" t="n">
+        <v>0.0754587142857143</v>
+      </c>
       <c r="AW96"/>
       <c r="AX96"/>
       <c r="AY96"/>
@@ -10192,11 +10192,11 @@
       <c r="BK96"/>
       <c r="BL96"/>
       <c r="BM96"/>
-      <c r="BN96" t="n">
+      <c r="BN96"/>
+      <c r="BO96"/>
+      <c r="BP96" t="n">
         <v>0</v>
       </c>
-      <c r="BO96"/>
-      <c r="BP96"/>
       <c r="BQ96"/>
       <c r="BR96"/>
     </row>
@@ -10211,7 +10211,7 @@
         <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0786617142857143</v>
+        <v>0.704196142857143</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -10220,7 +10220,7 @@
         <v>77</v>
       </c>
       <c r="G97" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H97" t="s">
         <v>80</v>
@@ -10247,11 +10247,11 @@
       <c r="X97"/>
       <c r="Y97"/>
       <c r="Z97"/>
-      <c r="AA97" t="n">
+      <c r="AA97"/>
+      <c r="AB97"/>
+      <c r="AC97" t="n">
         <v>5</v>
       </c>
-      <c r="AB97"/>
-      <c r="AC97"/>
       <c r="AD97"/>
       <c r="AE97"/>
       <c r="AF97"/>
@@ -10269,11 +10269,11 @@
       <c r="AR97"/>
       <c r="AS97"/>
       <c r="AT97"/>
-      <c r="AU97" t="n">
-        <v>0.0786617142857143</v>
-      </c>
+      <c r="AU97"/>
       <c r="AV97"/>
-      <c r="AW97"/>
+      <c r="AW97" t="n">
+        <v>0.704196142857143</v>
+      </c>
       <c r="AX97"/>
       <c r="AY97"/>
       <c r="AZ97"/>
@@ -10291,11 +10291,11 @@
       <c r="BL97"/>
       <c r="BM97"/>
       <c r="BN97"/>
-      <c r="BO97" t="n">
+      <c r="BO97"/>
+      <c r="BP97"/>
+      <c r="BQ97" t="n">
         <v>0</v>
       </c>
-      <c r="BP97"/>
-      <c r="BQ97"/>
       <c r="BR97"/>
     </row>
     <row r="98">
@@ -10309,7 +10309,7 @@
         <v>5</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0754587142857143</v>
+        <v>0.629783142857143</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -10318,7 +10318,7 @@
         <v>77</v>
       </c>
       <c r="G98" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H98" t="s">
         <v>73</v>
@@ -10346,11 +10346,11 @@
       <c r="Y98"/>
       <c r="Z98"/>
       <c r="AA98"/>
-      <c r="AB98" t="n">
+      <c r="AB98"/>
+      <c r="AC98"/>
+      <c r="AD98" t="n">
         <v>5</v>
       </c>
-      <c r="AC98"/>
-      <c r="AD98"/>
       <c r="AE98"/>
       <c r="AF98"/>
       <c r="AG98"/>
@@ -10368,11 +10368,11 @@
       <c r="AS98"/>
       <c r="AT98"/>
       <c r="AU98"/>
-      <c r="AV98" t="n">
-        <v>0.0754587142857143</v>
-      </c>
+      <c r="AV98"/>
       <c r="AW98"/>
-      <c r="AX98"/>
+      <c r="AX98" t="n">
+        <v>0.629783142857143</v>
+      </c>
       <c r="AY98"/>
       <c r="AZ98"/>
       <c r="BA98"/>
@@ -10390,11 +10390,11 @@
       <c r="BM98"/>
       <c r="BN98"/>
       <c r="BO98"/>
-      <c r="BP98" t="n">
+      <c r="BP98"/>
+      <c r="BQ98"/>
+      <c r="BR98" t="n">
         <v>0</v>
       </c>
-      <c r="BQ98"/>
-      <c r="BR98"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10404,19 +10404,19 @@
         <v>83</v>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>5.14285714285714</v>
       </c>
       <c r="D99" t="n">
-        <v>0.704196142857143</v>
+        <v>0.0916192857142857</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G99" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s">
         <v>80</v>
@@ -10435,7 +10435,9 @@
       <c r="P99"/>
       <c r="Q99"/>
       <c r="R99"/>
-      <c r="S99"/>
+      <c r="S99" t="n">
+        <v>5.14285714285714</v>
+      </c>
       <c r="T99"/>
       <c r="U99"/>
       <c r="V99"/>
@@ -10445,9 +10447,7 @@
       <c r="Z99"/>
       <c r="AA99"/>
       <c r="AB99"/>
-      <c r="AC99" t="n">
-        <v>5</v>
-      </c>
+      <c r="AC99"/>
       <c r="AD99"/>
       <c r="AE99"/>
       <c r="AF99"/>
@@ -10457,7 +10457,9 @@
       <c r="AJ99"/>
       <c r="AK99"/>
       <c r="AL99"/>
-      <c r="AM99"/>
+      <c r="AM99" t="n">
+        <v>0.0916192857142857</v>
+      </c>
       <c r="AN99"/>
       <c r="AO99"/>
       <c r="AP99"/>
@@ -10467,9 +10469,7 @@
       <c r="AT99"/>
       <c r="AU99"/>
       <c r="AV99"/>
-      <c r="AW99" t="n">
-        <v>0.704196142857143</v>
-      </c>
+      <c r="AW99"/>
       <c r="AX99"/>
       <c r="AY99"/>
       <c r="AZ99"/>
@@ -10479,7 +10479,9 @@
       <c r="BD99"/>
       <c r="BE99"/>
       <c r="BF99"/>
-      <c r="BG99"/>
+      <c r="BG99" t="n">
+        <v>0</v>
+      </c>
       <c r="BH99"/>
       <c r="BI99"/>
       <c r="BJ99"/>
@@ -10489,9 +10491,7 @@
       <c r="BN99"/>
       <c r="BO99"/>
       <c r="BP99"/>
-      <c r="BQ99" t="n">
-        <v>0</v>
-      </c>
+      <c r="BQ99"/>
       <c r="BR99"/>
     </row>
     <row r="100">
@@ -10502,19 +10502,19 @@
         <v>83</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>5.14285714285714</v>
       </c>
       <c r="D100" t="n">
-        <v>0.629783142857143</v>
+        <v>0.0860757142857143</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G100" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H100" t="s">
         <v>73</v>
@@ -10534,7 +10534,9 @@
       <c r="Q100"/>
       <c r="R100"/>
       <c r="S100"/>
-      <c r="T100"/>
+      <c r="T100" t="n">
+        <v>5.14285714285714</v>
+      </c>
       <c r="U100"/>
       <c r="V100"/>
       <c r="W100"/>
@@ -10544,9 +10546,7 @@
       <c r="AA100"/>
       <c r="AB100"/>
       <c r="AC100"/>
-      <c r="AD100" t="n">
-        <v>5</v>
-      </c>
+      <c r="AD100"/>
       <c r="AE100"/>
       <c r="AF100"/>
       <c r="AG100"/>
@@ -10556,7 +10556,9 @@
       <c r="AK100"/>
       <c r="AL100"/>
       <c r="AM100"/>
-      <c r="AN100"/>
+      <c r="AN100" t="n">
+        <v>0.0860757142857143</v>
+      </c>
       <c r="AO100"/>
       <c r="AP100"/>
       <c r="AQ100"/>
@@ -10566,9 +10568,7 @@
       <c r="AU100"/>
       <c r="AV100"/>
       <c r="AW100"/>
-      <c r="AX100" t="n">
-        <v>0.629783142857143</v>
-      </c>
+      <c r="AX100"/>
       <c r="AY100"/>
       <c r="AZ100"/>
       <c r="BA100"/>
@@ -10578,7 +10578,9 @@
       <c r="BE100"/>
       <c r="BF100"/>
       <c r="BG100"/>
-      <c r="BH100"/>
+      <c r="BH100" t="n">
+        <v>0</v>
+      </c>
       <c r="BI100"/>
       <c r="BJ100"/>
       <c r="BK100"/>
@@ -10588,9 +10590,7 @@
       <c r="BO100"/>
       <c r="BP100"/>
       <c r="BQ100"/>
-      <c r="BR100" t="n">
-        <v>0</v>
-      </c>
+      <c r="BR100"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10701,7 +10701,7 @@
         <v>5.57142857142857</v>
       </c>
       <c r="D102" t="n">
-        <v>0.105758571428571</v>
+        <v>0.105700571428571</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -10752,7 +10752,7 @@
       <c r="AK102"/>
       <c r="AL102"/>
       <c r="AM102" t="n">
-        <v>0.105758571428571</v>
+        <v>0.105700571428571</v>
       </c>
       <c r="AN102"/>
       <c r="AO102"/>
@@ -10796,22 +10796,22 @@
         <v>84</v>
       </c>
       <c r="C103" t="n">
-        <v>5.71428571428571</v>
+        <v>5.57142857142857</v>
       </c>
       <c r="D103" t="n">
-        <v>0.117169</v>
+        <v>0.100944428571429</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G103" t="s">
         <v>79</v>
       </c>
       <c r="H103" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -10819,9 +10819,7 @@
       <c r="J103" t="n">
         <v>7</v>
       </c>
-      <c r="K103" t="n">
-        <v>5.71428571428571</v>
-      </c>
+      <c r="K103"/>
       <c r="L103"/>
       <c r="M103"/>
       <c r="N103"/>
@@ -10830,7 +10828,9 @@
       <c r="Q103"/>
       <c r="R103"/>
       <c r="S103"/>
-      <c r="T103"/>
+      <c r="T103" t="n">
+        <v>5.57142857142857</v>
+      </c>
       <c r="U103"/>
       <c r="V103"/>
       <c r="W103"/>
@@ -10841,9 +10841,7 @@
       <c r="AB103"/>
       <c r="AC103"/>
       <c r="AD103"/>
-      <c r="AE103" t="n">
-        <v>0.117169</v>
-      </c>
+      <c r="AE103"/>
       <c r="AF103"/>
       <c r="AG103"/>
       <c r="AH103"/>
@@ -10852,7 +10850,9 @@
       <c r="AK103"/>
       <c r="AL103"/>
       <c r="AM103"/>
-      <c r="AN103"/>
+      <c r="AN103" t="n">
+        <v>0.100944428571429</v>
+      </c>
       <c r="AO103"/>
       <c r="AP103"/>
       <c r="AQ103"/>
@@ -10863,9 +10863,7 @@
       <c r="AV103"/>
       <c r="AW103"/>
       <c r="AX103"/>
-      <c r="AY103" t="n">
-        <v>0</v>
-      </c>
+      <c r="AY103"/>
       <c r="AZ103"/>
       <c r="BA103"/>
       <c r="BB103"/>
@@ -10874,7 +10872,9 @@
       <c r="BE103"/>
       <c r="BF103"/>
       <c r="BG103"/>
-      <c r="BH103"/>
+      <c r="BH103" t="n">
+        <v>0</v>
+      </c>
       <c r="BI103"/>
       <c r="BJ103"/>
       <c r="BK103"/>
@@ -10897,19 +10897,19 @@
         <v>5.71428571428571</v>
       </c>
       <c r="D104" t="n">
-        <v>0.100526428571429</v>
+        <v>0.117169</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G104" t="s">
         <v>79</v>
       </c>
       <c r="H104" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -10917,7 +10917,9 @@
       <c r="J104" t="n">
         <v>7</v>
       </c>
-      <c r="K104"/>
+      <c r="K104" t="n">
+        <v>5.71428571428571</v>
+      </c>
       <c r="L104"/>
       <c r="M104"/>
       <c r="N104"/>
@@ -10926,9 +10928,7 @@
       <c r="Q104"/>
       <c r="R104"/>
       <c r="S104"/>
-      <c r="T104" t="n">
-        <v>5.71428571428571</v>
-      </c>
+      <c r="T104"/>
       <c r="U104"/>
       <c r="V104"/>
       <c r="W104"/>
@@ -10939,7 +10939,9 @@
       <c r="AB104"/>
       <c r="AC104"/>
       <c r="AD104"/>
-      <c r="AE104"/>
+      <c r="AE104" t="n">
+        <v>0.117169</v>
+      </c>
       <c r="AF104"/>
       <c r="AG104"/>
       <c r="AH104"/>
@@ -10948,9 +10950,7 @@
       <c r="AK104"/>
       <c r="AL104"/>
       <c r="AM104"/>
-      <c r="AN104" t="n">
-        <v>0.100526428571429</v>
-      </c>
+      <c r="AN104"/>
       <c r="AO104"/>
       <c r="AP104"/>
       <c r="AQ104"/>
@@ -10961,7 +10961,9 @@
       <c r="AV104"/>
       <c r="AW104"/>
       <c r="AX104"/>
-      <c r="AY104"/>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ104"/>
       <c r="BA104"/>
       <c r="BB104"/>
@@ -10970,9 +10972,7 @@
       <c r="BE104"/>
       <c r="BF104"/>
       <c r="BG104"/>
-      <c r="BH104" t="n">
-        <v>0</v>
-      </c>
+      <c r="BH104"/>
       <c r="BI104"/>
       <c r="BJ104"/>
       <c r="BK104"/>
@@ -12695,16 +12695,16 @@
         <v>140</v>
       </c>
       <c r="D2" t="n">
-        <v>1.46428571428571</v>
+        <v>1.45</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>53.5714285714286</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>0.243439392857143</v>
+        <v>0.243354635714286</v>
       </c>
     </row>
     <row r="3">
@@ -12718,13 +12718,13 @@
         <v>140</v>
       </c>
       <c r="D3" t="n">
-        <v>1.68571428571429</v>
+        <v>1.7</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>46.4285714285714</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>0.25212195</v>
@@ -12732,16 +12732,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
         <v>140</v>
       </c>
       <c r="D4" t="n">
-        <v>3.45</v>
+        <v>3.44285714285714</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -12750,21 +12750,21 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.300786614285714</v>
+        <v>0.297248171428571</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="n">
         <v>140</v>
       </c>
       <c r="D5" t="n">
-        <v>3.45714285714286</v>
+        <v>3.45</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.297444028571429</v>
+        <v>0.300786614285714</v>
       </c>
     </row>
     <row r="6">
@@ -12787,7 +12787,7 @@
         <v>140</v>
       </c>
       <c r="D6" t="n">
-        <v>4.99285714285714</v>
+        <v>5.01428571428571</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>140</v>
       </c>
       <c r="D7" t="n">
-        <v>5.95</v>
+        <v>5.94285714285714</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.475307457142857</v>
+        <v>0.475325457142857</v>
       </c>
     </row>
   </sheetData>
@@ -12904,10 +12904,10 @@
         <v>78</v>
       </c>
       <c r="D4" t="n">
-        <v>1.39285714285714</v>
+        <v>1.46428571428571</v>
       </c>
       <c r="E4" t="n">
-        <v>60.7142857142857</v>
+        <v>53.5714285714286</v>
       </c>
       <c r="F4" t="n">
         <v>0.249396785714286</v>
@@ -12995,10 +12995,10 @@
         <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>1.22857142857143</v>
+        <v>1.25714285714286</v>
       </c>
       <c r="E2" t="n">
-        <v>77.1428571428572</v>
+        <v>74.2857142857143</v>
       </c>
       <c r="F2" t="n">
         <v>0.0528084428571429</v>
@@ -13066,10 +13066,10 @@
         <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>1.41428571428571</v>
       </c>
       <c r="E2" t="n">
-        <v>64.2857142857143</v>
+        <v>62.8571428571429</v>
       </c>
       <c r="F2" t="n">
         <v>0.249749742857143</v>
@@ -13086,13 +13086,13 @@
         <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>1.28571428571429</v>
+        <v>1.27142857142857</v>
       </c>
       <c r="E3" t="n">
-        <v>71.4285714285714</v>
+        <v>72.8571428571428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.236994914285714</v>
+        <v>0.2369128</v>
       </c>
     </row>
   </sheetData>
@@ -24947,7 +24947,7 @@
         <v>75</v>
       </c>
       <c r="D339" t="n">
-        <v>0.179815</v>
+        <v>0.177324</v>
       </c>
       <c r="E339" t="n">
         <v>2</v>
@@ -25008,16 +25008,16 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B341" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C341" t="s">
         <v>75</v>
       </c>
       <c r="D341" t="n">
-        <v>0.288093</v>
+        <v>0.284438</v>
       </c>
       <c r="E341" t="n">
         <v>4</v>
@@ -25043,16 +25043,16 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B342" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C342" t="s">
         <v>75</v>
       </c>
       <c r="D342" t="n">
-        <v>0.29223</v>
+        <v>0.288093</v>
       </c>
       <c r="E342" t="n">
         <v>5</v>
@@ -25087,7 +25087,7 @@
         <v>75</v>
       </c>
       <c r="D343" t="n">
-        <v>0.362975</v>
+        <v>0.365324</v>
       </c>
       <c r="E343" t="n">
         <v>6</v>
@@ -25157,7 +25157,7 @@
         <v>75</v>
       </c>
       <c r="D345" t="n">
-        <v>0.06886</v>
+        <v>0.067612</v>
       </c>
       <c r="E345" t="n">
         <v>2</v>
@@ -25227,7 +25227,7 @@
         <v>75</v>
       </c>
       <c r="D347" t="n">
-        <v>0.101477</v>
+        <v>0.09879</v>
       </c>
       <c r="E347" t="n">
         <v>4</v>
@@ -25297,7 +25297,7 @@
         <v>75</v>
       </c>
       <c r="D349" t="n">
-        <v>0.141724</v>
+        <v>0.140651</v>
       </c>
       <c r="E349" t="n">
         <v>6</v>
@@ -25367,7 +25367,7 @@
         <v>75</v>
       </c>
       <c r="D351" t="n">
-        <v>0.039893</v>
+        <v>0.039282</v>
       </c>
       <c r="E351" t="n">
         <v>2</v>
@@ -25437,7 +25437,7 @@
         <v>75</v>
       </c>
       <c r="D353" t="n">
-        <v>0.054013</v>
+        <v>0.052899</v>
       </c>
       <c r="E353" t="n">
         <v>4</v>
@@ -25472,7 +25472,7 @@
         <v>75</v>
       </c>
       <c r="D354" t="n">
-        <v>0.064481</v>
+        <v>0.063603</v>
       </c>
       <c r="E354" t="n">
         <v>5</v>
@@ -25577,7 +25577,7 @@
         <v>75</v>
       </c>
       <c r="D357" t="n">
-        <v>0.042912</v>
+        <v>0.042168</v>
       </c>
       <c r="E357" t="n">
         <v>2</v>
@@ -25647,7 +25647,7 @@
         <v>75</v>
       </c>
       <c r="D359" t="n">
-        <v>0.060394</v>
+        <v>0.059299</v>
       </c>
       <c r="E359" t="n">
         <v>4</v>
@@ -25682,7 +25682,7 @@
         <v>75</v>
       </c>
       <c r="D360" t="n">
-        <v>0.069752</v>
+        <v>0.068077</v>
       </c>
       <c r="E360" t="n">
         <v>5</v>
@@ -25743,16 +25743,16 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B362" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C362" t="s">
         <v>75</v>
       </c>
       <c r="D362" t="n">
-        <v>0.05061</v>
+        <v>0.049927</v>
       </c>
       <c r="E362" t="n">
         <v>1</v>
@@ -25778,16 +25778,16 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B363" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C363" t="s">
         <v>75</v>
       </c>
       <c r="D363" t="n">
-        <v>0.05101</v>
+        <v>0.05061</v>
       </c>
       <c r="E363" t="n">
         <v>2</v>
@@ -25822,7 +25822,7 @@
         <v>75</v>
       </c>
       <c r="D364" t="n">
-        <v>0.064884</v>
+        <v>0.062834</v>
       </c>
       <c r="E364" t="n">
         <v>3</v>
@@ -25892,7 +25892,7 @@
         <v>75</v>
       </c>
       <c r="D366" t="n">
-        <v>0.083601</v>
+        <v>0.082428</v>
       </c>
       <c r="E366" t="n">
         <v>5</v>
@@ -25997,7 +25997,7 @@
         <v>75</v>
       </c>
       <c r="D369" t="n">
-        <v>0.004539</v>
+        <v>0.004588</v>
       </c>
       <c r="E369" t="n">
         <v>2</v>
@@ -26102,7 +26102,7 @@
         <v>75</v>
       </c>
       <c r="D372" t="n">
-        <v>0.007709</v>
+        <v>0.008029</v>
       </c>
       <c r="E372" t="n">
         <v>5</v>
@@ -26137,7 +26137,7 @@
         <v>75</v>
       </c>
       <c r="D373" t="n">
-        <v>0.010119</v>
+        <v>0.011062</v>
       </c>
       <c r="E373" t="n">
         <v>6</v>
@@ -26207,7 +26207,7 @@
         <v>75</v>
       </c>
       <c r="D375" t="n">
-        <v>0.002348</v>
+        <v>0.002358</v>
       </c>
       <c r="E375" t="n">
         <v>2</v>
@@ -26312,7 +26312,7 @@
         <v>75</v>
       </c>
       <c r="D378" t="n">
-        <v>0.004566</v>
+        <v>0.004522</v>
       </c>
       <c r="E378" t="n">
         <v>5</v>
@@ -26347,7 +26347,7 @@
         <v>75</v>
       </c>
       <c r="D379" t="n">
-        <v>0.007658</v>
+        <v>0.008759</v>
       </c>
       <c r="E379" t="n">
         <v>6</v>
@@ -26417,7 +26417,7 @@
         <v>75</v>
       </c>
       <c r="D381" t="n">
-        <v>0.177678</v>
+        <v>0.175109</v>
       </c>
       <c r="E381" t="n">
         <v>2</v>
@@ -26478,16 +26478,16 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B383" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C383" t="s">
         <v>75</v>
       </c>
       <c r="D383" t="n">
-        <v>0.267731</v>
+        <v>0.263809</v>
       </c>
       <c r="E383" t="n">
         <v>4</v>
@@ -26513,16 +26513,16 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B384" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C384" t="s">
         <v>75</v>
       </c>
       <c r="D384" t="n">
-        <v>0.270734</v>
+        <v>0.267731</v>
       </c>
       <c r="E384" t="n">
         <v>5</v>
@@ -26557,7 +26557,7 @@
         <v>75</v>
       </c>
       <c r="D385" t="n">
-        <v>0.338737</v>
+        <v>0.343432</v>
       </c>
       <c r="E385" t="n">
         <v>6</v>
@@ -26627,7 +26627,7 @@
         <v>75</v>
       </c>
       <c r="D387" t="n">
-        <v>0.06799</v>
+        <v>0.066843</v>
       </c>
       <c r="E387" t="n">
         <v>2</v>
@@ -26697,7 +26697,7 @@
         <v>75</v>
       </c>
       <c r="D389" t="n">
-        <v>0.095857</v>
+        <v>0.093474</v>
       </c>
       <c r="E389" t="n">
         <v>4</v>
@@ -26767,7 +26767,7 @@
         <v>75</v>
       </c>
       <c r="D391" t="n">
-        <v>0.133623</v>
+        <v>0.133223</v>
       </c>
       <c r="E391" t="n">
         <v>6</v>
@@ -26793,16 +26793,16 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B392" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C392" t="s">
         <v>75</v>
       </c>
       <c r="D392" t="n">
-        <v>0.039114</v>
+        <v>0.038811</v>
       </c>
       <c r="E392" t="n">
         <v>1</v>
@@ -26828,16 +26828,16 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B393" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C393" t="s">
         <v>75</v>
       </c>
       <c r="D393" t="n">
-        <v>0.0393</v>
+        <v>0.039114</v>
       </c>
       <c r="E393" t="n">
         <v>2</v>
@@ -26907,7 +26907,7 @@
         <v>75</v>
       </c>
       <c r="D395" t="n">
-        <v>0.052137</v>
+        <v>0.051136</v>
       </c>
       <c r="E395" t="n">
         <v>4</v>
@@ -26942,7 +26942,7 @@
         <v>75</v>
       </c>
       <c r="D396" t="n">
-        <v>0.064349</v>
+        <v>0.063556</v>
       </c>
       <c r="E396" t="n">
         <v>5</v>
@@ -27047,7 +27047,7 @@
         <v>75</v>
       </c>
       <c r="D399" t="n">
-        <v>0.042139</v>
+        <v>0.041482</v>
       </c>
       <c r="E399" t="n">
         <v>2</v>
@@ -27117,7 +27117,7 @@
         <v>75</v>
       </c>
       <c r="D401" t="n">
-        <v>0.055811</v>
+        <v>0.054842</v>
       </c>
       <c r="E401" t="n">
         <v>4</v>
@@ -27143,16 +27143,16 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B402" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C402" t="s">
         <v>75</v>
       </c>
       <c r="D402" t="n">
-        <v>0.065899</v>
+        <v>0.065453</v>
       </c>
       <c r="E402" t="n">
         <v>5</v>
@@ -27178,16 +27178,16 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B403" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C403" t="s">
         <v>75</v>
       </c>
       <c r="D403" t="n">
-        <v>0.066741</v>
+        <v>0.065899</v>
       </c>
       <c r="E403" t="n">
         <v>6</v>
@@ -27222,7 +27222,7 @@
         <v>75</v>
       </c>
       <c r="D404" t="n">
-        <v>0.050405</v>
+        <v>0.049463</v>
       </c>
       <c r="E404" t="n">
         <v>1</v>
@@ -27292,7 +27292,7 @@
         <v>75</v>
       </c>
       <c r="D406" t="n">
-        <v>0.062767</v>
+        <v>0.060853</v>
       </c>
       <c r="E406" t="n">
         <v>3</v>
@@ -27362,7 +27362,7 @@
         <v>75</v>
       </c>
       <c r="D408" t="n">
-        <v>0.083443</v>
+        <v>0.0824</v>
       </c>
       <c r="E408" t="n">
         <v>5</v>
@@ -27467,7 +27467,7 @@
         <v>75</v>
       </c>
       <c r="D411" t="n">
-        <v>0.004519</v>
+        <v>0.004569</v>
       </c>
       <c r="E411" t="n">
         <v>2</v>
@@ -27572,7 +27572,7 @@
         <v>75</v>
       </c>
       <c r="D414" t="n">
-        <v>0.007401</v>
+        <v>0.007692</v>
       </c>
       <c r="E414" t="n">
         <v>5</v>
@@ -27607,7 +27607,7 @@
         <v>75</v>
       </c>
       <c r="D415" t="n">
-        <v>0.009672</v>
+        <v>0.010478</v>
       </c>
       <c r="E415" t="n">
         <v>6</v>
@@ -27677,7 +27677,7 @@
         <v>75</v>
       </c>
       <c r="D417" t="n">
-        <v>0.002349</v>
+        <v>0.002355</v>
       </c>
       <c r="E417" t="n">
         <v>2</v>
@@ -27782,7 +27782,7 @@
         <v>75</v>
       </c>
       <c r="D420" t="n">
-        <v>0.004415</v>
+        <v>0.004358</v>
       </c>
       <c r="E420" t="n">
         <v>5</v>
@@ -27817,7 +27817,7 @@
         <v>75</v>
       </c>
       <c r="D421" t="n">
-        <v>0.00712</v>
+        <v>0.008069</v>
       </c>
       <c r="E421" t="n">
         <v>6</v>
